--- a/Invision/reports/excel/EyeExamDateSearch.xlsx
+++ b/Invision/reports/excel/EyeExamDateSearch.xlsx
@@ -104,43 +104,43 @@
     <t>9910223344</t>
   </si>
   <si>
+    <t>IH-IVC-26-0388</t>
+  </si>
+  <si>
+    <t>SONAM</t>
+  </si>
+  <si>
+    <t>MALE</t>
+  </si>
+  <si>
+    <t>13Y 2M</t>
+  </si>
+  <si>
+    <t>MOHAN</t>
+  </si>
+  <si>
+    <t>8343485853</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>IH-IVC-26-0387</t>
+  </si>
+  <si>
+    <t>RABI DD</t>
+  </si>
+  <si>
+    <t>RAJA DD</t>
+  </si>
+  <si>
+    <t>REFERRAL</t>
+  </si>
+  <si>
+    <t>875643873</t>
+  </si>
+  <si>
     <t>In-Progress</t>
-  </si>
-  <si>
-    <t>IH-IVC-26-0388</t>
-  </si>
-  <si>
-    <t>SONAM</t>
-  </si>
-  <si>
-    <t>MALE</t>
-  </si>
-  <si>
-    <t>13Y 2M</t>
-  </si>
-  <si>
-    <t>MOHAN</t>
-  </si>
-  <si>
-    <t>8343485853</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>IH-IVC-26-0387</t>
-  </si>
-  <si>
-    <t>RABI DD</t>
-  </si>
-  <si>
-    <t>RAJA DD</t>
-  </si>
-  <si>
-    <t>REFERRAL</t>
-  </si>
-  <si>
-    <t>875643873</t>
   </si>
   <si>
     <t>IH-IVC-26-0386</t>
@@ -445,7 +445,7 @@
         <v>17</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>19</v>
@@ -453,31 +453,31 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="C5" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="D5" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="E5" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="E5" t="s" s="0">
+      <c r="F5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="F5" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s" s="0">
+      <c r="H5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s" s="0">
-        <v>37</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>19</v>
@@ -485,31 +485,31 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>39</v>
-      </c>
       <c r="C6" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>27</v>
       </c>
       <c r="E6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="F6" t="s" s="0">
+      <c r="G6" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="G6" t="s" s="0">
+      <c r="H6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s" s="0">
         <v>42</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s" s="0">
-        <v>30</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>19</v>
@@ -523,7 +523,7 @@
         <v>44</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>45</v>
@@ -541,7 +541,7 @@
         <v>17</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>19</v>
@@ -555,7 +555,7 @@
         <v>48</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>49</v>
@@ -564,7 +564,7 @@
         <v>48</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>50</v>
@@ -573,7 +573,7 @@
         <v>17</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>19</v>
@@ -619,7 +619,7 @@
         <v>57</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>58</v>
@@ -628,7 +628,7 @@
         <v>57</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>59</v>
@@ -669,7 +669,7 @@
         <v>17</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s" s="0">
         <v>19</v>
@@ -683,7 +683,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>66</v>
@@ -733,7 +733,7 @@
         <v>17</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="J13" t="s" s="0">
         <v>19</v>
@@ -747,7 +747,7 @@
         <v>74</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>75</v>
@@ -765,7 +765,7 @@
         <v>17</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" t="s" s="0">
         <v>19</v>
@@ -779,7 +779,7 @@
         <v>79</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>80</v>
@@ -811,7 +811,7 @@
         <v>84</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>85</v>
@@ -820,7 +820,7 @@
         <v>86</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>87</v>
